--- a/research/traditional_assets/database/data/papua_new_guinea/papua_new_guinea_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/papua_new_guinea/papua_new_guinea_metals_mining.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0106</v>
+        <v>-0.0567</v>
       </c>
       <c r="G2">
-        <v>-1.307017543859649</v>
+        <v>-1.432432432432432</v>
       </c>
       <c r="H2">
-        <v>-1.307017543859649</v>
+        <v>-1.432432432432432</v>
       </c>
       <c r="I2">
-        <v>-1.087719298245614</v>
+        <v>-1.594594594594595</v>
       </c>
       <c r="J2">
-        <v>-1.087719298245614</v>
+        <v>-1.594594594594595</v>
       </c>
       <c r="K2">
-        <v>-1.52</v>
+        <v>-1.84</v>
       </c>
       <c r="L2">
-        <v>-1.333333333333333</v>
+        <v>-1.657657657657658</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.476</v>
+        <v>0.195</v>
       </c>
       <c r="V2">
-        <v>0.005354330708661417</v>
+        <v>0.002044025157232704</v>
       </c>
       <c r="W2">
-        <v>-0.05868725868725869</v>
+        <v>-0.05227272727272727</v>
       </c>
       <c r="X2">
-        <v>0.1108635021478781</v>
+        <v>0.2106031744425516</v>
       </c>
       <c r="Y2">
-        <v>-0.1695507608351368</v>
+        <v>-0.2628759017152788</v>
       </c>
       <c r="Z2">
-        <v>0.04589926319603817</v>
+        <v>0.03173695496783417</v>
       </c>
       <c r="AA2">
-        <v>-0.04992551435358537</v>
+        <v>-0.05060757684060042</v>
       </c>
       <c r="AB2">
-        <v>0.1107047701736257</v>
+        <v>0.210358647918171</v>
       </c>
       <c r="AC2">
-        <v>-0.1606302845272111</v>
+        <v>-0.2609662247587714</v>
       </c>
       <c r="AD2">
-        <v>0.251</v>
+        <v>0.235</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.251</v>
+        <v>0.235</v>
       </c>
       <c r="AG2">
-        <v>-0.225</v>
+        <v>0.03999999999999998</v>
       </c>
       <c r="AH2">
-        <v>0.002815447947863736</v>
+        <v>0.002457259371568986</v>
       </c>
       <c r="AI2">
-        <v>0.00708019519900708</v>
+        <v>0.007956661587946504</v>
       </c>
       <c r="AJ2">
-        <v>-0.002537355511700028</v>
+        <v>0.0004191114836546519</v>
       </c>
       <c r="AK2">
-        <v>-0.006433166547533952</v>
+        <v>0.001363326516700749</v>
       </c>
       <c r="AL2">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="AM2">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="AN2">
-        <v>-0.2127118644067797</v>
+        <v>-0.1390532544378698</v>
       </c>
       <c r="AO2">
-        <v>-53.91304347826087</v>
+        <v>-104.1176470588235</v>
       </c>
       <c r="AP2">
-        <v>0.1906779661016949</v>
+        <v>-0.02366863905325443</v>
       </c>
       <c r="AQ2">
-        <v>-53.91304347826087</v>
+        <v>-104.1176470588235</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0106</v>
+        <v>-0.0567</v>
       </c>
       <c r="G3">
-        <v>-1.307017543859649</v>
+        <v>-1.432432432432432</v>
       </c>
       <c r="H3">
-        <v>-1.307017543859649</v>
+        <v>-1.432432432432432</v>
       </c>
       <c r="I3">
-        <v>-1.087719298245614</v>
+        <v>-1.594594594594595</v>
       </c>
       <c r="J3">
-        <v>-1.087719298245614</v>
+        <v>-1.594594594594595</v>
       </c>
       <c r="K3">
-        <v>-1.52</v>
+        <v>-1.84</v>
       </c>
       <c r="L3">
-        <v>-1.333333333333333</v>
+        <v>-1.657657657657658</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.476</v>
+        <v>0.195</v>
       </c>
       <c r="V3">
-        <v>0.005354330708661417</v>
+        <v>0.002044025157232704</v>
       </c>
       <c r="W3">
-        <v>-0.05868725868725869</v>
+        <v>-0.05227272727272727</v>
       </c>
       <c r="X3">
-        <v>0.1108635021478781</v>
+        <v>0.2106031744425516</v>
       </c>
       <c r="Y3">
-        <v>-0.1695507608351368</v>
+        <v>-0.2628759017152788</v>
       </c>
       <c r="Z3">
-        <v>0.04589926319603817</v>
+        <v>0.03173695496783417</v>
       </c>
       <c r="AA3">
-        <v>-0.04992551435358537</v>
+        <v>-0.05060757684060042</v>
       </c>
       <c r="AB3">
-        <v>0.1107047701736257</v>
+        <v>0.210358647918171</v>
       </c>
       <c r="AC3">
-        <v>-0.1606302845272111</v>
+        <v>-0.2609662247587714</v>
       </c>
       <c r="AD3">
-        <v>0.251</v>
+        <v>0.235</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.251</v>
+        <v>0.235</v>
       </c>
       <c r="AG3">
-        <v>-0.225</v>
+        <v>0.03999999999999998</v>
       </c>
       <c r="AH3">
-        <v>0.002815447947863736</v>
+        <v>0.002457259371568986</v>
       </c>
       <c r="AI3">
-        <v>0.00708019519900708</v>
+        <v>0.007956661587946504</v>
       </c>
       <c r="AJ3">
-        <v>-0.002537355511700028</v>
+        <v>0.0004191114836546519</v>
       </c>
       <c r="AK3">
-        <v>-0.006433166547533952</v>
+        <v>0.001363326516700749</v>
       </c>
       <c r="AL3">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="AM3">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="AN3">
-        <v>-0.2127118644067797</v>
+        <v>-0.1390532544378698</v>
       </c>
       <c r="AO3">
-        <v>-53.91304347826087</v>
+        <v>-104.1176470588235</v>
       </c>
       <c r="AP3">
-        <v>0.1906779661016949</v>
+        <v>-0.02366863905325443</v>
       </c>
       <c r="AQ3">
-        <v>-53.91304347826087</v>
+        <v>-104.1176470588235</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/papua_new_guinea/papua_new_guinea_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/papua_new_guinea/papua_new_guinea_metals_mining.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0567</v>
+        <v>-0.122</v>
       </c>
       <c r="G2">
-        <v>-1.432432432432432</v>
+        <v>-1.610619469026549</v>
       </c>
       <c r="H2">
-        <v>-1.432432432432432</v>
+        <v>-1.610619469026549</v>
       </c>
       <c r="I2">
-        <v>-1.594594594594595</v>
+        <v>-1.769911504424779</v>
       </c>
       <c r="J2">
-        <v>-1.594594594594595</v>
+        <v>-1.769911504424779</v>
       </c>
       <c r="K2">
-        <v>-1.84</v>
+        <v>-2.07</v>
       </c>
       <c r="L2">
-        <v>-1.657657657657658</v>
+        <v>-1.831858407079646</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,55 +630,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.195</v>
+        <v>0.114</v>
       </c>
       <c r="V2">
-        <v>0.002044025157232704</v>
+        <v>0.001225806451612903</v>
       </c>
       <c r="W2">
-        <v>-0.05227272727272727</v>
+        <v>-0.07064846416382252</v>
       </c>
       <c r="X2">
-        <v>0.2106031744425516</v>
+        <v>0.1633317397320595</v>
       </c>
       <c r="Y2">
-        <v>-0.2628759017152788</v>
+        <v>-0.233980203895882</v>
       </c>
       <c r="Z2">
-        <v>0.03173695496783417</v>
+        <v>0.03851397409679618</v>
       </c>
       <c r="AA2">
-        <v>-0.05060757684060042</v>
+        <v>-0.0681663258350375</v>
       </c>
       <c r="AB2">
-        <v>0.210358647918171</v>
+        <v>0.1632581214672175</v>
       </c>
       <c r="AC2">
-        <v>-0.2609662247587714</v>
+        <v>-0.231424447302255</v>
       </c>
       <c r="AD2">
-        <v>0.235</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.235</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AG2">
-        <v>0.03999999999999998</v>
+        <v>-0.02700000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.002457259371568986</v>
+        <v>0.0009346095587998323</v>
       </c>
       <c r="AI2">
-        <v>0.007956661587946504</v>
+        <v>0.00348181054148157</v>
       </c>
       <c r="AJ2">
-        <v>0.0004191114836546519</v>
+        <v>-0.0002904068923235779</v>
       </c>
       <c r="AK2">
-        <v>0.001363326516700749</v>
+        <v>-0.001085514413219154</v>
       </c>
       <c r="AL2">
         <v>0.017</v>
@@ -687,16 +687,16 @@
         <v>0.017</v>
       </c>
       <c r="AN2">
-        <v>-0.1390532544378698</v>
+        <v>-0.04438775510204081</v>
       </c>
       <c r="AO2">
-        <v>-104.1176470588235</v>
+        <v>-117.6470588235294</v>
       </c>
       <c r="AP2">
-        <v>-0.02366863905325443</v>
+        <v>0.01377551020408164</v>
       </c>
       <c r="AQ2">
-        <v>-104.1176470588235</v>
+        <v>-117.6470588235294</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0567</v>
+        <v>-0.122</v>
       </c>
       <c r="G3">
-        <v>-1.432432432432432</v>
+        <v>-1.610619469026549</v>
       </c>
       <c r="H3">
-        <v>-1.432432432432432</v>
+        <v>-1.610619469026549</v>
       </c>
       <c r="I3">
-        <v>-1.594594594594595</v>
+        <v>-1.769911504424779</v>
       </c>
       <c r="J3">
-        <v>-1.594594594594595</v>
+        <v>-1.769911504424779</v>
       </c>
       <c r="K3">
-        <v>-1.84</v>
+        <v>-2.07</v>
       </c>
       <c r="L3">
-        <v>-1.657657657657658</v>
+        <v>-1.831858407079646</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.195</v>
+        <v>0.114</v>
       </c>
       <c r="V3">
-        <v>0.002044025157232704</v>
+        <v>0.001225806451612903</v>
       </c>
       <c r="W3">
-        <v>-0.05227272727272727</v>
+        <v>-0.07064846416382252</v>
       </c>
       <c r="X3">
-        <v>0.2106031744425516</v>
+        <v>0.1633317397320595</v>
       </c>
       <c r="Y3">
-        <v>-0.2628759017152788</v>
+        <v>-0.233980203895882</v>
       </c>
       <c r="Z3">
-        <v>0.03173695496783417</v>
+        <v>0.03851397409679618</v>
       </c>
       <c r="AA3">
-        <v>-0.05060757684060042</v>
+        <v>-0.0681663258350375</v>
       </c>
       <c r="AB3">
-        <v>0.210358647918171</v>
+        <v>0.1632581214672175</v>
       </c>
       <c r="AC3">
-        <v>-0.2609662247587714</v>
+        <v>-0.231424447302255</v>
       </c>
       <c r="AD3">
-        <v>0.235</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.235</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AG3">
-        <v>0.03999999999999998</v>
+        <v>-0.02700000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.002457259371568986</v>
+        <v>0.0009346095587998323</v>
       </c>
       <c r="AI3">
-        <v>0.007956661587946504</v>
+        <v>0.00348181054148157</v>
       </c>
       <c r="AJ3">
-        <v>0.0004191114836546519</v>
+        <v>-0.0002904068923235779</v>
       </c>
       <c r="AK3">
-        <v>0.001363326516700749</v>
+        <v>-0.001085514413219154</v>
       </c>
       <c r="AL3">
         <v>0.017</v>
@@ -815,16 +815,16 @@
         <v>0.017</v>
       </c>
       <c r="AN3">
-        <v>-0.1390532544378698</v>
+        <v>-0.04438775510204081</v>
       </c>
       <c r="AO3">
-        <v>-104.1176470588235</v>
+        <v>-117.6470588235294</v>
       </c>
       <c r="AP3">
-        <v>-0.02366863905325443</v>
+        <v>0.01377551020408164</v>
       </c>
       <c r="AQ3">
-        <v>-104.1176470588235</v>
+        <v>-117.6470588235294</v>
       </c>
     </row>
   </sheetData>
